--- a/artfynd/A 57949-2025 artfynd.xlsx
+++ b/artfynd/A 57949-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120530520</v>
+        <v>120530514</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>524567</v>
+        <v>524792</v>
       </c>
       <c r="R2" t="n">
-        <v>7113156</v>
+        <v>7113208</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120530516</v>
+        <v>120530515</v>
       </c>
       <c r="B3" t="n">
-        <v>90644</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>524832</v>
+        <v>524980</v>
       </c>
       <c r="R3" t="n">
-        <v>7113183</v>
+        <v>7113177</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120530517</v>
+        <v>120530516</v>
       </c>
       <c r="B4" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>524823</v>
+        <v>524832</v>
       </c>
       <c r="R4" t="n">
-        <v>7113170</v>
+        <v>7113183</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120530518</v>
+        <v>120530517</v>
       </c>
       <c r="B5" t="n">
-        <v>79579</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>524775</v>
+        <v>524823</v>
       </c>
       <c r="R5" t="n">
-        <v>7113160</v>
+        <v>7113170</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120530514</v>
+        <v>120530518</v>
       </c>
       <c r="B6" t="n">
-        <v>91119</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>524792</v>
+        <v>524775</v>
       </c>
       <c r="R6" t="n">
-        <v>7113208</v>
+        <v>7113160</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,12 +1163,7 @@
         <v>120530513</v>
       </c>
       <c r="B7" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,108 +1254,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>120530515</v>
-      </c>
-      <c r="B8" t="n">
-        <v>79676</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Ringvattnet, Jmt</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>524980</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7113177</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Alanäs</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57949-2025 artfynd.xlsx
+++ b/artfynd/A 57949-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120530514</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120530515</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120530516</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120530517</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120530518</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,8 +1284,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120530513</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>